--- a/data/trans_orig/P19D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19D-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2007</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1899</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10370</t>
+          <t>10407</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1047</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10275</t>
+          <t>10277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>574968</t>
+          <t>571184</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>610723</t>
+          <t>609979</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>83,3%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>834446</t>
+          <t>833632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>872666</t>
+          <t>872989</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,02%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1420651</t>
+          <t>1419420</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1473623</t>
+          <t>1475288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,46%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3741</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16066</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5037</t>
+          <t>4784</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>18022</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11098</t>
+          <t>10995</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>28881</t>
+          <t>27393</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1049,7 +1049,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70764</t>
+          <t>74036</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107028</t>
+          <t>111651</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74678</t>
+          <t>74376</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110644</t>
+          <t>110718</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152289</t>
+          <t>154309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>204132</t>
+          <t>207682</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6361</t>
+          <t>5308</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6692</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9078</t>
+          <t>9562</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,03%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,36%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1195239</t>
+          <t>1196989</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1234533</t>
+          <t>1233744</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,86%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1245056</t>
+          <t>1246964</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1284366</t>
+          <t>1284380</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,7 +1465,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2452013</t>
+          <t>2455075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2508392</t>
+          <t>2508642</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14028</t>
+          <t>13568</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34317</t>
+          <t>34243</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,47 +1543,47 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
+          <t>1,03%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>23280</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>14638</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>35126</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,7%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>23280</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>15171</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>36440</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>34102</t>
+          <t>33399</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>61695</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>57609</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>92008</t>
+          <t>91430</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>64863</t>
+          <t>65038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101044</t>
+          <t>99295</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>132569</t>
+          <t>131863</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>179844</t>
+          <t>180263</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8080</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6616</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>397720</t>
+          <t>398454</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>422496</t>
+          <t>423196</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>93,54%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>367146</t>
+          <t>368856</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>388906</t>
+          <t>389075</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>89,81%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,18%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>772732</t>
+          <t>772481</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>806542</t>
+          <t>806058</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17026</t>
+          <t>16602</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37576</t>
+          <t>37241</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9879</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26816</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30159</t>
+          <t>30168</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56013</t>
+          <t>56332</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8084</t>
+          <t>8202</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26762</t>
+          <t>25772</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6084</t>
+          <t>6448</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>20689</t>
+          <t>19370</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17072</t>
+          <t>17417</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39898</t>
+          <t>39159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,55%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2576</t>
+          <t>2552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15530</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4534</t>
+          <t>4549</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17903</t>
+          <t>16988</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,7 +2530,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2191445</t>
+          <t>2190757</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2253268</t>
+          <t>2249704</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,19%</t>
+          <t>89,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2471115</t>
+          <t>2467496</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2531552</t>
+          <t>2527200</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4680531</t>
+          <t>4677526</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4763510</t>
+          <t>4758395</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,54%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>72124</t>
+          <t>73089</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37845</t>
+          <t>37393</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67775</t>
+          <t>66076</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>88227</t>
+          <t>85682</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>129118</t>
+          <t>127078</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>148770</t>
+          <t>151457</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203077</t>
+          <t>203230</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158520</t>
+          <t>159488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211288</t>
+          <t>211701</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>325731</t>
+          <t>327531</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>399121</t>
+          <t>397914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -3045,7 +3045,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2012</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2012 (tasa de respuesta: 99,65%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5056</t>
+          <t>4467</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,62 +3275,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2058</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,05%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5666</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,27%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>533596</t>
+          <t>534787</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>586410</t>
+          <t>584549</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,39%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>907369</t>
+          <t>907511</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>959666</t>
+          <t>958629</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,34%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1459020</t>
+          <t>1459540</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1530374</t>
+          <t>1531146</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>80,18%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6501</t>
+          <t>7140</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21210</t>
+          <t>21088</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12464</t>
+          <t>12840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>31516</t>
+          <t>32350</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>23322</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45630</t>
+          <t>47163</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>182484</t>
+          <t>183254</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>233935</t>
+          <t>230734</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>151843</t>
+          <t>151520</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200424</t>
+          <t>200764</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>347715</t>
+          <t>346611</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>417825</t>
+          <t>414720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,72%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7801</t>
+          <t>6502</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,7 +3829,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,62 +3844,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>1290</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2067</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>6485</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>1290</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>8634</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,2%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1418395</t>
+          <t>1419316</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1479792</t>
+          <t>1478229</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,27%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1374395</t>
+          <t>1372553</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1427443</t>
+          <t>1425687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,59%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,93%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2808850</t>
+          <t>2810087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2893040</t>
+          <t>2888239</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,31%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45603</t>
+          <t>44529</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79529</t>
+          <t>77583</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25440</t>
+          <t>25868</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51892</t>
+          <t>52060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>78108</t>
+          <t>76296</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>121129</t>
+          <t>120300</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147311</t>
+          <t>146976</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>201111</t>
+          <t>197497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,82 +4163,82 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>8,73%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>147642</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>126191</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>174612</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>11,0%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>319894</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>286049</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>355367</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>9,78%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
           <t>8,75%</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>147642</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>124613</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>174784</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,3%</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>7,85%</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>11,01%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>294</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>319894</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>282674</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>356596</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>9,78%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,87%</t>
         </is>
       </c>
     </row>
@@ -4378,97 +4378,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>2130</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>2124</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>384866</t>
+          <t>384052</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>411056</t>
+          <t>410359</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,48%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>364261</t>
+          <t>361307</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>391296</t>
+          <t>390035</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>86,16%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>755899</t>
+          <t>756789</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>794504</t>
+          <t>795255</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15580</t>
+          <t>15323</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38301</t>
+          <t>36563</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>15186</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37265</t>
+          <t>37466</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34733</t>
+          <t>34871</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>66886</t>
+          <t>65008</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8011</t>
+          <t>8472</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24520</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13171</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31808</t>
+          <t>31999</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24200</t>
+          <t>24673</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>49315</t>
+          <t>50305</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7526</t>
+          <t>7858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,62 +4982,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2300</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2073</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>7643</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,04%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2300</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>7389</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2367554</t>
+          <t>2367455</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2453293</t>
+          <t>2448351</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5080,7 +5080,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2671464</t>
+          <t>2675392</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2751185</t>
+          <t>2754085</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5063787</t>
+          <t>5061264</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5182046</t>
+          <t>5182167</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,7 +5145,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>76637</t>
+          <t>77506</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119480</t>
+          <t>119384</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62577</t>
+          <t>63059</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>100687</t>
+          <t>102161</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150756</t>
+          <t>150306</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>208801</t>
+          <t>209081</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>354437</t>
+          <t>360147</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>434018</t>
+          <t>432925</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>311061</t>
+          <t>309073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>378430</t>
+          <t>380267</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>686760</t>
+          <t>683640</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>793962</t>
+          <t>792219</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,32%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -5552,7 +5552,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2016</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2016 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7283</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,62 +5782,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2057</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2103</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6215</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>6164</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374891</t>
+          <t>374346</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404477</t>
+          <t>404017</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>533739</t>
+          <t>532130</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>569738</t>
+          <t>568084</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>917872</t>
+          <t>917110</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>965400</t>
+          <t>963196</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>87,96%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>863</t>
+          <t>866</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8211</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>10377</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1883</t>
+          <t>1896</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>14177</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48214</t>
+          <t>48702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77056</t>
+          <t>77818</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65059</t>
+          <t>66019</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>100761</t>
+          <t>101947</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>123213</t>
+          <t>122914</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167653</t>
+          <t>168641</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>7329</t>
+          <t>5575</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,62 +6351,62 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>4524</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,03%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>992</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>5950</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,03%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,13%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1475295</t>
+          <t>1472890</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1527006</t>
+          <t>1531011</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1484730</t>
+          <t>1484924</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1539352</t>
+          <t>1537391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2976403</t>
+          <t>2976109</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3051486</t>
+          <t>3051109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,42%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,63%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13563</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33670</t>
+          <t>35041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>34706</t>
+          <t>35192</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62046</t>
+          <t>62937</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>53371</t>
+          <t>52844</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>88509</t>
+          <t>87758</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>147313</t>
+          <t>144466</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>196780</t>
+          <t>195851</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126714</t>
+          <t>127959</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174079</t>
+          <t>172943</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,12%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>285006</t>
+          <t>285592</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>354822</t>
+          <t>354673</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
@@ -6885,82 +6885,82 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2084</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5550</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,09%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6247</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>443150</t>
+          <t>443048</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>468376</t>
+          <t>468792</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>430866</t>
+          <t>429069</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>460114</t>
+          <t>459559</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>879928</t>
+          <t>882745</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>920872</t>
+          <t>922911</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,48%</t>
+          <t>91,68%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17469</t>
+          <t>17640</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38418</t>
+          <t>38887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27061</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>51184</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51076</t>
+          <t>49412</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83376</t>
+          <t>83816</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>23356</t>
+          <t>24306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>14531</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>32862</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27352</t>
+          <t>26429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>52805</t>
+          <t>50317</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9140</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6634</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1041</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10435</t>
+          <t>9454</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7544,7 +7544,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,17%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2313387</t>
+          <t>2316776</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2380129</t>
+          <t>2385982</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2478854</t>
+          <t>2469191</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2547245</t>
+          <t>2544546</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,5%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4814936</t>
+          <t>4812945</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4911710</t>
+          <t>4906764</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,12%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39038</t>
+          <t>39335</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>69530</t>
+          <t>68761</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71828</t>
+          <t>70394</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>107483</t>
+          <t>108971</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117799</t>
+          <t>117495</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>167502</t>
+          <t>166625</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>219164</t>
+          <t>217086</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>278817</t>
+          <t>277820</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>224700</t>
+          <t>225656</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>284802</t>
+          <t>287661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>456696</t>
+          <t>459899</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>543825</t>
+          <t>541733</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -8059,7 +8059,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el tipo de dentista que consultó en 2023</t>
+          <t>Población según a dónde pertenecía el último dentista al que consultó en 2023 (tasa de respuesta: 99,6%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8254,97 +8254,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1432</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1013</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,14%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1148</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>379861</t>
+          <t>377983</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>410340</t>
+          <t>408368</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>613029</t>
+          <t>612890</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>645302</t>
+          <t>646871</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,62%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1002754</t>
+          <t>1003254</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1047865</t>
+          <t>1047318</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>83,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -8485,7 +8485,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8746</t>
+          <t>9287</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2241</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9456</t>
+          <t>9706</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4535</t>
+          <t>4707</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14348</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70035</t>
+          <t>70967</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99555</t>
+          <t>101799</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74022</t>
+          <t>73539</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>106834</t>
+          <t>107974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>151749</t>
+          <t>152265</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196018</t>
+          <t>195964</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,7 +8678,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -8823,97 +8823,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2226</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1481</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>0,07%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1782</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1212104</t>
+          <t>1345332</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2043177</t>
+          <t>2044111</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,12 +8951,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,32%</t>
+          <t>60,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2072337</t>
+          <t>2073980</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2125225</t>
+          <t>2127177</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3174416</t>
+          <t>3186991</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4154141</t>
+          <t>4154358</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,81%</t>
         </is>
       </c>
     </row>
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13975</t>
+          <t>13977</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39472</t>
+          <t>37732</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9069,7 +9069,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>22135</t>
+          <t>23133</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9104,7 +9104,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24346</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>52994</t>
+          <t>53078</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>161949</t>
+          <t>160102</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1015070</t>
+          <t>869421</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>38,96%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>63804</t>
+          <t>61599</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110649</t>
+          <t>110065</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>238053</t>
+          <t>237042</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1217842</t>
+          <t>1217147</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>27,48%</t>
         </is>
       </c>
     </row>
@@ -9392,97 +9392,97 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>1485</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,12%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>570954</t>
+          <t>571550</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>600387</t>
+          <t>601086</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,43%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>608466</t>
+          <t>609919</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>628072</t>
+          <t>629546</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1188738</t>
+          <t>1189838</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1223297</t>
+          <t>1225109</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17639</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40755</t>
+          <t>40259</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12402</t>
+          <t>11886</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27234</t>
+          <t>27122</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34192</t>
+          <t>34011</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61085</t>
+          <t>62086</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,83%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10235</t>
+          <t>9368</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29639</t>
+          <t>27679</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22652</t>
+          <t>22796</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>21826</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45303</t>
+          <t>45021</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -9961,97 +9961,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>1572</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,02%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2130685</t>
+          <t>2102443</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3022528</t>
+          <t>3029566</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3312555</t>
+          <t>3312894</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3388304</t>
+          <t>3386464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5348119</t>
+          <t>5347598</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6384354</t>
+          <t>6386443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,26%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>37736</t>
+          <t>39022</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>74679</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>26219</t>
+          <t>25527</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48249</t>
+          <t>49162</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10237,12 +10237,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71612</t>
+          <t>70984</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>114959</t>
+          <t>115774</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10277,7 +10277,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>267011</t>
+          <t>259073</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1169165</t>
+          <t>1161880</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,94%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>158393</t>
+          <t>157463</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>225484</t>
+          <t>222211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>443848</t>
+          <t>442909</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1494271</t>
+          <t>1515124</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,89%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19D-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P19D-Estudios-trans_orig.xlsx
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1046</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10407</t>
+          <t>10093</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1047</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10277</t>
+          <t>10358</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>571184</t>
+          <t>575178</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>609979</t>
+          <t>610378</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>83,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,38%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>833632</t>
+          <t>834063</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>872989</t>
+          <t>873068</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1419420</t>
+          <t>1417306</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1475288</t>
+          <t>1472647</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>86,07%</t>
+          <t>85,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,3%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3812</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>16715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4784</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18022</t>
+          <t>18513</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10995</t>
+          <t>10778</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>27393</t>
+          <t>28474</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>74036</t>
+          <t>72368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111651</t>
+          <t>105622</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74376</t>
+          <t>73431</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>110718</t>
+          <t>110993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>154309</t>
+          <t>156364</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207682</t>
+          <t>206325</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,51%</t>
         </is>
       </c>
     </row>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>6330</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>5901</t>
+          <t>6704</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>905</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>9562</t>
+          <t>8416</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,03%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,31%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1196989</t>
+          <t>1194356</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1233744</t>
+          <t>1235239</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1246964</t>
+          <t>1247056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1284380</t>
+          <t>1286530</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2455075</t>
+          <t>2454274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2508642</t>
+          <t>2509903</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,39%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13568</t>
+          <t>14337</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34243</t>
+          <t>33968</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>14638</t>
+          <t>14917</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>35126</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33399</t>
+          <t>33071</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61695</t>
+          <t>61188</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>57609</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91430</t>
+          <t>91811</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>65038</t>
+          <t>65569</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99295</t>
+          <t>100387</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>131863</t>
+          <t>131609</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>180263</t>
+          <t>179210</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -1876,7 +1876,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1911,7 +1911,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>6733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1961,7 +1961,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>398454</t>
+          <t>397327</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>423196</t>
+          <t>423382</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,58%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>368856</t>
+          <t>367631</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>389075</t>
+          <t>388689</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>89,93%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>772481</t>
+          <t>773567</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>806058</t>
+          <t>806575</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>16602</t>
+          <t>16220</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37241</t>
+          <t>35267</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9808</t>
+          <t>9903</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26043</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>30168</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56332</t>
+          <t>55477</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,44%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8202</t>
+          <t>7592</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6448</t>
+          <t>6277</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>19370</t>
+          <t>20843</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17417</t>
+          <t>16181</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39159</t>
+          <t>38727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>870</t>
+          <t>868</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>7030</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2552</t>
+          <t>2868</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>14463</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,47 +2490,47 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>9431</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>4793</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>18052</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
           <t>0,09%</t>
         </is>
       </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>9431</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>16988</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,09%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,35%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2190757</t>
+          <t>2192652</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2249704</t>
+          <t>2250311</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2467496</t>
+          <t>2467197</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2527200</t>
+          <t>2525577</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4677526</t>
+          <t>4677792</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4758395</t>
+          <t>4762543</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,62%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>42197</t>
+          <t>42953</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>73089</t>
+          <t>73623</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37393</t>
+          <t>38099</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>66076</t>
+          <t>66273</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>85682</t>
+          <t>83012</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127078</t>
+          <t>126249</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>151457</t>
+          <t>154159</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203230</t>
+          <t>204118</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>159488</t>
+          <t>159527</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>211701</t>
+          <t>212697</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>327531</t>
+          <t>323118</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>397914</t>
+          <t>399839</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -3245,7 +3245,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4467</t>
+          <t>6896</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3315,7 +3315,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>5060</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>534787</t>
+          <t>533985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>584549</t>
+          <t>584120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>907511</t>
+          <t>910493</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>958629</t>
+          <t>961929</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1459540</t>
+          <t>1455904</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1531146</t>
+          <t>1530301</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,13%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7140</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>21088</t>
+          <t>21385</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>32350</t>
+          <t>31761</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23322</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>47163</t>
+          <t>45934</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,41%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>183254</t>
+          <t>183048</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>230734</t>
+          <t>231899</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>23,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>151520</t>
+          <t>148928</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>200764</t>
+          <t>199063</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,78%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>346611</t>
+          <t>345923</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>414720</t>
+          <t>417216</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -3814,7 +3814,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6502</t>
+          <t>6492</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6472</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1419316</t>
+          <t>1419090</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1478229</t>
+          <t>1478624</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1372553</t>
+          <t>1375582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1425687</t>
+          <t>1429832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,47%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2810087</t>
+          <t>2815648</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>2888239</t>
+          <t>2892260</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>88,44%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44529</t>
+          <t>44524</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77583</t>
+          <t>79823</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>25868</t>
+          <t>25729</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52060</t>
+          <t>52110</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>76296</t>
+          <t>77508</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>120300</t>
+          <t>121622</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>146976</t>
+          <t>147952</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>197497</t>
+          <t>201719</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>126191</t>
+          <t>123921</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>174612</t>
+          <t>173897</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>286049</t>
+          <t>287066</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>355367</t>
+          <t>353531</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,81%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>384052</t>
+          <t>384791</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>410359</t>
+          <t>411729</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>361307</t>
+          <t>363538</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>390035</t>
+          <t>390347</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,99%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>756789</t>
+          <t>756658</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>795255</t>
+          <t>796901</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>87,82%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>92,28%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>15323</t>
+          <t>15351</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36563</t>
+          <t>37949</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>15186</t>
+          <t>15177</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>37466</t>
+          <t>38549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34871</t>
+          <t>34714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>65008</t>
+          <t>65522</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8472</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25803</t>
+          <t>24902</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13171</t>
+          <t>12633</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31999</t>
+          <t>29906</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24673</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50305</t>
+          <t>49456</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,74%</t>
         </is>
       </c>
     </row>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7858</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7643</t>
+          <t>8645</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5037,7 +5037,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2367455</t>
+          <t>2367891</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2448351</t>
+          <t>2451905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>84,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2675392</t>
+          <t>2674499</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2754085</t>
+          <t>2753986</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,22%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5061264</t>
+          <t>5068531</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5182167</t>
+          <t>5181666</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,77%</t>
+          <t>85,76%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>77506</t>
+          <t>79048</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>119384</t>
+          <t>124067</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>63059</t>
+          <t>62476</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>102161</t>
+          <t>102333</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>150306</t>
+          <t>151688</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>209081</t>
+          <t>210830</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,49%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>360147</t>
+          <t>357212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>432925</t>
+          <t>432433</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>309073</t>
+          <t>309521</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>380267</t>
+          <t>379838</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>683640</t>
+          <t>682916</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>792219</t>
+          <t>784398</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>12,98%</t>
         </is>
       </c>
     </row>
@@ -5752,7 +5752,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>6508</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5767,7 +5767,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6215</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5837,7 +5837,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,59%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>374346</t>
+          <t>374154</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>404017</t>
+          <t>404317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>532130</t>
+          <t>535873</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>568084</t>
+          <t>571188</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>84,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>917110</t>
+          <t>918475</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>963196</t>
+          <t>966865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,96%</t>
+          <t>88,3%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>866</t>
+          <t>861</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5993,7 +5993,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10377</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1896</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14177</t>
+          <t>13014</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>48702</t>
+          <t>48965</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77818</t>
+          <t>77787</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66019</t>
+          <t>64951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101947</t>
+          <t>99103</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122914</t>
+          <t>121330</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>168641</t>
+          <t>168418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5575</t>
+          <t>4984</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>4981</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6406,7 +6406,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,15%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1472890</t>
+          <t>1474083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1531011</t>
+          <t>1527985</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1484924</t>
+          <t>1482512</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1537391</t>
+          <t>1537348</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2976109</t>
+          <t>2977807</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3051109</t>
+          <t>3052180</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,66%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>13563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>35041</t>
+          <t>32972</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35192</t>
+          <t>34877</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62937</t>
+          <t>64702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>52844</t>
+          <t>54247</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>87758</t>
+          <t>88202</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>144466</t>
+          <t>145159</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>195851</t>
+          <t>196697</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>127959</t>
+          <t>126348</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>172943</t>
+          <t>174832</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>285592</t>
+          <t>284705</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>354673</t>
+          <t>352587</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,36%</t>
         </is>
       </c>
     </row>
@@ -6925,7 +6925,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>5550</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6940,7 +6940,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6960,7 +6960,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5520</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6975,7 +6975,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>443048</t>
+          <t>443509</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>468792</t>
+          <t>468678</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>429069</t>
+          <t>430449</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>459559</t>
+          <t>459622</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>84,41%</t>
+          <t>84,68%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>90,41%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>882745</t>
+          <t>881299</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>922911</t>
+          <t>920817</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17640</t>
+          <t>17438</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38887</t>
+          <t>39739</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>26488</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>51880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49412</t>
+          <t>50139</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>83816</t>
+          <t>83497</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,29%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24306</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14531</t>
+          <t>15147</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>33696</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>26429</t>
+          <t>27082</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>50317</t>
+          <t>52493</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,21%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9166</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7494,7 +7494,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>6134</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7509,7 +7509,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1041</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9593</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2316776</t>
+          <t>2314673</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2385982</t>
+          <t>2380309</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,99%</t>
+          <t>89,78%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2469191</t>
+          <t>2471403</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2544546</t>
+          <t>2544749</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>86,5%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4812945</t>
+          <t>4811370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4906764</t>
+          <t>4913057</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,23%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39335</t>
+          <t>38115</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>68761</t>
+          <t>68136</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>70394</t>
+          <t>69105</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108971</t>
+          <t>109915</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>117495</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>166625</t>
+          <t>166056</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7770,7 +7770,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>217086</t>
+          <t>219393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>277820</t>
+          <t>276911</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>225656</t>
+          <t>225347</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>287661</t>
+          <t>286693</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>459899</t>
+          <t>454943</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>541733</t>
+          <t>545444</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,91%</t>
         </is>
       </c>
     </row>
@@ -8362,17 +8362,17 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>395631</t>
+          <t>438869</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>377983</t>
+          <t>421481</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408368</t>
+          <t>454197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,5%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8397,32 +8397,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>631977</t>
+          <t>688923</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>612890</t>
+          <t>674024</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>646871</t>
+          <t>702493</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>85,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,29%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8432,32 +8432,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1027608</t>
+          <t>1127792</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1003254</t>
+          <t>1105391</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1047318</t>
+          <t>1148577</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,58%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,85%</t>
         </is>
       </c>
     </row>
@@ -8475,67 +8475,67 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3914</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1514</t>
+          <t>1744</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9287</t>
+          <t>10291</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>5068</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2454</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>10063</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
           <t>0,31%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4800</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2241</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9706</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8545,17 +8545,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>8714</t>
+          <t>9503</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>5418</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14423</t>
+          <t>16388</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -8588,32 +8588,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>83745</t>
+          <t>92791</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70967</t>
+          <t>77381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101799</t>
+          <t>110409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8623,32 +8623,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>87714</t>
+          <t>92452</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>73539</t>
+          <t>78417</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>107974</t>
+          <t>107096</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8658,32 +8658,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>171459</t>
+          <t>185244</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>152265</t>
+          <t>165682</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>195964</t>
+          <t>206736</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,63%</t>
         </is>
       </c>
     </row>
@@ -8701,17 +8701,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>483290</t>
+          <t>536095</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>483290</t>
+          <t>536095</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>483290</t>
+          <t>536095</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8736,17 +8736,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>724491</t>
+          <t>786444</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>724491</t>
+          <t>786444</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>724491</t>
+          <t>786444</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8771,17 +8771,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1207781</t>
+          <t>1322539</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1207781</t>
+          <t>1322539</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1207781</t>
+          <t>1322539</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8931,32 +8931,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>1808979</t>
+          <t>1944862</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1345332</t>
+          <t>1911942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2044111</t>
+          <t>1976348</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8966,32 +8966,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>2096481</t>
+          <t>1989270</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2073980</t>
+          <t>1968125</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2127177</t>
+          <t>2007867</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>93,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9001,32 +9001,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>3905460</t>
+          <t>3934132</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3186991</t>
+          <t>3892519</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4154358</t>
+          <t>3972191</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,19%</t>
+          <t>92,44%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,33%</t>
         </is>
       </c>
     </row>
@@ -9044,32 +9044,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>23960</t>
+          <t>27782</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13977</t>
+          <t>18507</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>37732</t>
+          <t>42622</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9079,32 +9079,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12509</t>
+          <t>17465</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>10675</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>23133</t>
+          <t>31203</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9114,32 +9114,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>36468</t>
+          <t>45248</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>32316</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>53078</t>
+          <t>63263</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -9157,32 +9157,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>398437</t>
+          <t>173735</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>160102</t>
+          <t>143133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>869421</t>
+          <t>204392</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9192,32 +9192,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>88281</t>
+          <t>102959</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>61599</t>
+          <t>86393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110065</t>
+          <t>121979</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9227,32 +9227,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>486718</t>
+          <t>276693</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>237042</t>
+          <t>243540</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1217147</t>
+          <t>318685</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
     </row>
@@ -9270,17 +9270,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2231376</t>
+          <t>2146379</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2231376</t>
+          <t>2146379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2231376</t>
+          <t>2146379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9305,17 +9305,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2197270</t>
+          <t>2109694</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2197270</t>
+          <t>2109694</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2197270</t>
+          <t>2109694</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9340,17 +9340,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4428646</t>
+          <t>4256073</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4428646</t>
+          <t>4256073</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4428646</t>
+          <t>4256073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9500,32 +9500,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>587480</t>
+          <t>650819</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>571550</t>
+          <t>632197</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>601086</t>
+          <t>665290</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,6%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>90,43%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9535,32 +9535,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>620157</t>
+          <t>688642</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>609919</t>
+          <t>677237</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>629546</t>
+          <t>697491</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9570,32 +9570,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1207637</t>
+          <t>1339461</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1189838</t>
+          <t>1318200</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1225109</t>
+          <t>1355177</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,72%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,82%</t>
         </is>
       </c>
     </row>
@@ -9613,32 +9613,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>27285</t>
+          <t>29320</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>17639</t>
+          <t>19006</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>44379</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9648,32 +9648,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18618</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11886</t>
+          <t>14942</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27122</t>
+          <t>31342</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9683,32 +9683,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>45903</t>
+          <t>51240</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>34011</t>
+          <t>39260</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62086</t>
+          <t>67850</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -9726,32 +9726,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9368</t>
+          <t>13501</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>38345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9761,32 +9761,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22796</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9796,32 +9796,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>38532</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>21826</t>
+          <t>27856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>45021</t>
+          <t>54257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -9839,17 +9839,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>632020</t>
+          <t>702793</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9874,17 +9874,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>653556</t>
+          <t>726440</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>653556</t>
+          <t>726440</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>653556</t>
+          <t>726440</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9909,17 +9909,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1285576</t>
+          <t>1429233</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1285576</t>
+          <t>1429233</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1285576</t>
+          <t>1429233</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -10069,32 +10069,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2792090</t>
+          <t>3034550</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2102443</t>
+          <t>2993651</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>3029566</t>
+          <t>3071879</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>83,43%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,82%</t>
+          <t>88,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10104,32 +10104,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>3348616</t>
+          <t>3366836</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3312894</t>
+          <t>3339027</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3386464</t>
+          <t>3395310</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10139,32 +10139,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>6140705</t>
+          <t>6401385</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5347598</t>
+          <t>6354373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6386443</t>
+          <t>6446461</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>91,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,99%</t>
         </is>
       </c>
     </row>
@@ -10182,32 +10182,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>55159</t>
+          <t>61538</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>39022</t>
+          <t>46282</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>75369</t>
+          <t>80889</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10217,32 +10217,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>35927</t>
+          <t>44453</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>25527</t>
+          <t>32939</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>49162</t>
+          <t>58498</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10252,32 +10252,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>91086</t>
+          <t>105991</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>70984</t>
+          <t>85063</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>115774</t>
+          <t>129703</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -10295,32 +10295,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>499437</t>
+          <t>289180</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>259073</t>
+          <t>252612</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1161880</t>
+          <t>327406</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10330,32 +10330,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>190775</t>
+          <t>211289</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>157463</t>
+          <t>188765</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>222211</t>
+          <t>238456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10365,32 +10365,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>690212</t>
+          <t>500469</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>442909</t>
+          <t>458658</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1515124</t>
+          <t>541857</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>7,73%</t>
         </is>
       </c>
     </row>
@@ -10408,17 +10408,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3346686</t>
+          <t>3385267</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3346686</t>
+          <t>3385267</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3346686</t>
+          <t>3385267</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10443,17 +10443,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3575317</t>
+          <t>3622578</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3575317</t>
+          <t>3622578</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3575317</t>
+          <t>3622578</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10478,17 +10478,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6922003</t>
+          <t>7007845</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6922003</t>
+          <t>7007845</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6922003</t>
+          <t>7007845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
